--- a/projects/AcuRev1320/demand_test/20260701/Demand_2E3WN/demand_test_res_20260701170656/Fixed_Demand_Test_2E3WN_20260701170656.xlsx
+++ b/projects/AcuRev1320/demand_test/20260701/Demand_2E3WN/demand_test_res_20260701170656/Fixed_Demand_Test_2E3WN_20260701170656.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,18 +413,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>case</t>
+          <t>test_case</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>demand_accuracy</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -445,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>freq</t>
+          <t>freq(Hz)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -455,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>demand_method</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -470,12 +469,232 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>demand_trigger</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>结果</t>
+          <t>std_p_sys_1st</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>demand_p_sys_1st</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>std_q_sys_1st</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>demand_q_sys_1st</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>std_s_sys_1st</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>demand_s_sys_1st</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>std_ia_sys_1st</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>demand_ia_sys_1st</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>std_ib_sys_1st</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>demand_ib_sys_1st</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>std_ic_sys_1st</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>demand_ic_sys_1st</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>std_in_sys_1st</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>demand_in_sys_1st</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>is_pass_1st</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>std_p_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>demand_p_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>std_q_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>demand_q_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>std_s_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>demand_s_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>std_ia_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>demand_ia_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>std_ib_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>demand_ib_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>std_ic_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>demand_ic_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>std_in_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>demand_in_sys_2nd</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>is_pass_2nd</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>std_p_sys_3rd</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>demand_p_sys_3rd</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>std_q_sys_3rd</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>demand_q_sys_3rd</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>std_s_sys_3rd</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>demand_s_sys_3rd</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>std_ia_sys_3rd</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>demand_ia_sys_3rd</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>std_ib_sys_3rd</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>demand_ib_sys_3rd</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>std_ic_sys_3rd</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>demand_ic_sys_3rd</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>std_in_sys_3rd</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>demand_in_sys_3rd</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>is_pass_3rd</t>
         </is>
       </c>
     </row>
@@ -515,274 +734,29 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AcuRev1320_case2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="L2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.7999892234802246</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-9.545000648358837e-05</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.7999899983406067</v>
+      </c>
+      <c r="R2" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AC4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>case</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>周期</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>voltage</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>angle</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>interval</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>trigger</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>P(kW)_std</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>P(kW)_实测</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>P(kW)_误差%</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Q(kvar)_std</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Q(kvar)_实测</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Q(kvar)_误差%</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>S(kVA)_std</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>S(kVA)_实测</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>S(kVA)_误差%</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Ia(A)_std</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Ia(A)_实测</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Ia(A)_误差%</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Ib(A)_std</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Ib(A)_实测</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Ib(A)_误差%</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Ic(A)_std</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Ic(A)_实测</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Ic(A)_误差%</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>In(A)_std</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>In(A)_实测</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>In(A)_误差%</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AcuRev1320_case1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.79999</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-0.0001</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.79999</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.00002</v>
-      </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.000018835067749</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
@@ -791,172 +765,64 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-100</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1.99993109703064</v>
       </c>
       <c r="X2" t="n">
-        <v>1.99993</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="b">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AcuRev1320_case1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>200</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
         <v>0.5</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.49803</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4e-05</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="AB2" t="n">
+        <v>0.4980307519435883</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.281425572116859e-05</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0.5</v>
       </c>
-      <c r="O3" t="n">
-        <v>0.49803</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="AF2" t="n">
+        <v>0.498034805059433</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.5</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.49772</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="AH2" t="n">
+        <v>1.497724294662476</v>
+      </c>
+      <c r="AI2" t="n">
         <v>1.5</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.5</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.4963</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AcuRev1320_case2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>清零</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
+      <c r="AL2" t="n">
+        <v>1.496296167373657</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
